--- a/student_data/Students.xlsx
+++ b/student_data/Students.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>student_id</t>
   </si>
@@ -37,43 +37,34 @@
     <t>course</t>
   </si>
   <si>
-    <t>Bonda</t>
-  </si>
-  <si>
-    <t>Giriprasad</t>
-  </si>
-  <si>
-    <t>bonda.giri@gmail.com</t>
+    <t>Afiz</t>
+  </si>
+  <si>
+    <t>Ali</t>
+  </si>
+  <si>
+    <t>afiz.ali@gmail.com</t>
+  </si>
+  <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>Post Graduate</t>
+  </si>
+  <si>
+    <t>MSc International Project Management (with Advanced Practice)</t>
+  </si>
+  <si>
+    <t>Surya</t>
+  </si>
+  <si>
+    <t>Suresh</t>
+  </si>
+  <si>
+    <t>surya.suresh@gmail.com</t>
   </si>
   <si>
     <t>India</t>
-  </si>
-  <si>
-    <t>Post Graduate</t>
-  </si>
-  <si>
-    <t>MSc International Project Management (with Advanced Practice)</t>
-  </si>
-  <si>
-    <t>Afiz</t>
-  </si>
-  <si>
-    <t>Ali</t>
-  </si>
-  <si>
-    <t>afiz.ali@gmail.com</t>
-  </si>
-  <si>
-    <t>Bangladesh</t>
-  </si>
-  <si>
-    <t>Surya</t>
-  </si>
-  <si>
-    <t>Suresh</t>
-  </si>
-  <si>
-    <t>surya.suresh@gmail.com</t>
   </si>
   <si>
     <t>MSc Digital Marketing (with Advanced Practice)</t>
@@ -121,14 +112,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -141,12 +131,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -160,28 +165,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -208,28 +210,28 @@
         <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="0000FF"/>
@@ -485,19 +487,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +509,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -520,119 +522,96 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
-      <c r="A2" s="1">
-        <v>1234</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="3">
+        <v>10145419</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
-      <c r="A3" s="1">
-        <v>10145419</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="3">
+        <v>10195309</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
+      <c r="G3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
-      <c r="A4" s="1">
-        <v>10195309</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="3">
+        <v>10325808</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="D4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="3">
+        <v>10445379</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
-      <c r="A5" s="1">
-        <v>10325808</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
-      <c r="A6" s="1">
-        <v>10445379</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
